--- a/教育訓練教材/backend/chat_logs.xlsx
+++ b/教育訓練教材/backend/chat_logs.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="20" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -758,6 +758,57 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:07:41</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BPM一般費用報銷單_私車公用操作流程.md</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>如何申請高鐵費用</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>您好！很高興為您說明。根據您目前研讀的【BPM一般費用報銷單_私車公用操作流程.md】教材內容，申請高鐵費用是屬於國內出差交通費用的一部分，且需要獨立新增明細喔！
+以下是申請高鐵費用的具體步驟要點：
+---
+### **如何申請高鐵費用 (費用類別：A01)**
+高鐵車資與私車公用里程費是不同性質的費用，在 BPM 系統中需**分開新增明細**。
+1.  **進入 BPM 一般費用報銷單：**
+    *   透過 BPM 左側選單或「流程處理頁」進入「一般費用報銷單」。
+    *   建立新單後，請先完成「表頭資料」的填寫。
+2.  **帶入出差登記資料：**
+    *   在「費用明細區」中點選「出差登記單號」旁的查詢按鈕。
+    *   選擇對應的出差登記資料，並確認欄位資訊無誤。
+3.  **新增高鐵費用明細：**
+    *   在「費用明細」頁籤下，點選「**新增**」按鈕。
+    *   **費用類別：** 請選擇 **A01「國內出差－交通－高鐵」**。
+    *   **憑證日期：** 填寫高鐵票或電子發票上的日期。
+    *   **報銷金額：** 填寫實際支付的金額。
+    *   **發票類型、稅別碼、發票號碼與原幣稅額：** 依據您的票據資料詳細填寫。
+    *   **費用說明：** 建議填寫「高鐵（起訖站／出差事由）」，以便審核人員快速了解。
+    *   填妥後，點選「新增」按鈕將資料寫入費用明細列表。
+4.  **準備與上傳證明文件：**
+    *   請務必保留**完整的高鐵票或電子發票憑證**，這是申請的必要證明文件。
+    *   完成所有費用明細填寫後，在表單中找到「上傳所有相關附件」的功能，將高鐵票或電子發票的掃描/照片檔上傳至系統。
+5.  **儲存、送出與繳交正本：**
+    *   確認所有資訊及附件無誤後，儲存並送出簽核。
+    *   列印報銷單，並將**高鐵票或電子發票正本**及所有佐證資料依規定時間與方式交給人事單位。
+---
+**重要提醒：**
+*   **分項清楚：** 高鐵車資（A01）必須與私車公用里程費（A05）、高速公路通行費/ETag（A07）、停車費（A06）等**分開新增明細項目**。
+*   **憑證齊全：** 線上上傳的附件與紙本繳交的正本必須一致，且需保留完整憑證。
+若您在操作過程中遇到任何困難或有進一步的疑問，歡迎隨時再提出！</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
